--- a/FASE 1/Evidencias Grupales/Gantt CAPSTONE - SISTEMA DE GESTION PARA TRANSPORTE DE PASAJEROS.xlsx
+++ b/FASE 1/Evidencias Grupales/Gantt CAPSTONE - SISTEMA DE GESTION PARA TRANSPORTE DE PASAJEROS.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\capstone-2026\FASE 1\Evidencias Grupales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D5B373-F735-4516-A216-8CD2DEB8FD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500733D6-3ECF-4E6A-B5DE-32ADB553163D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gestión Proyecto Carta Gantt" sheetId="3" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gestión Proyecto Carta Gantt'!$D$1:$D$45</definedName>
+  </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1512,6 +1515,30 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1530,12 +1557,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1545,12 +1566,6 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1560,12 +1575,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1573,12 +1582,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1897,86 +1900,86 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="85"/>
-      <c r="L7" s="85"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="85"/>
-      <c r="Q7" s="85"/>
-      <c r="R7" s="85"/>
-      <c r="S7" s="85"/>
-      <c r="T7" s="85"/>
-      <c r="U7" s="85"/>
-      <c r="V7" s="85"/>
-      <c r="W7" s="85"/>
-      <c r="X7" s="85"/>
-      <c r="Y7" s="85"/>
-      <c r="Z7" s="85"/>
-      <c r="AA7" s="85"/>
-      <c r="AB7" s="86"/>
-      <c r="AC7" s="89"/>
-      <c r="AD7" s="90"/>
-      <c r="AE7" s="90"/>
-      <c r="AF7" s="90"/>
-      <c r="AG7" s="90"/>
-      <c r="AH7" s="90"/>
-      <c r="AI7" s="90"/>
-      <c r="AJ7" s="90"/>
-      <c r="AK7" s="90"/>
-      <c r="AL7" s="90"/>
-      <c r="AM7" s="90"/>
-      <c r="AN7" s="90"/>
-      <c r="AO7" s="90"/>
-      <c r="AP7" s="90"/>
-      <c r="AQ7" s="90"/>
-      <c r="AR7" s="90"/>
-      <c r="AS7" s="90"/>
-      <c r="AT7" s="90"/>
-      <c r="AU7" s="90"/>
-      <c r="AV7" s="91"/>
-      <c r="AW7" s="94"/>
-      <c r="AX7" s="95"/>
-      <c r="AY7" s="95"/>
-      <c r="AZ7" s="95"/>
-      <c r="BA7" s="95"/>
-      <c r="BB7" s="95"/>
-      <c r="BC7" s="95"/>
-      <c r="BD7" s="95"/>
-      <c r="BE7" s="95"/>
-      <c r="BF7" s="95"/>
-      <c r="BG7" s="95"/>
-      <c r="BH7" s="95"/>
-      <c r="BI7" s="95"/>
-      <c r="BJ7" s="95"/>
-      <c r="BK7" s="95"/>
-      <c r="BL7" s="95"/>
-      <c r="BM7" s="95"/>
-      <c r="BN7" s="95"/>
-      <c r="BO7" s="95"/>
-      <c r="BP7" s="96"/>
-      <c r="BQ7" s="99"/>
-      <c r="BR7" s="100"/>
-      <c r="BS7" s="100"/>
-      <c r="BT7" s="100"/>
-      <c r="BU7" s="100"/>
-      <c r="BV7" s="100"/>
-      <c r="BW7" s="100"/>
-      <c r="BX7" s="100"/>
-      <c r="BY7" s="100"/>
-      <c r="BZ7" s="100"/>
-      <c r="CA7" s="100"/>
-      <c r="CB7" s="100"/>
-      <c r="CC7" s="100"/>
-      <c r="CD7" s="100"/>
-      <c r="CE7" s="100"/>
-      <c r="CF7" s="100"/>
-      <c r="CG7" s="100"/>
-      <c r="CH7" s="100"/>
-      <c r="CI7" s="100"/>
-      <c r="CJ7" s="101"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="93"/>
+      <c r="P7" s="93"/>
+      <c r="Q7" s="93"/>
+      <c r="R7" s="93"/>
+      <c r="S7" s="93"/>
+      <c r="T7" s="93"/>
+      <c r="U7" s="93"/>
+      <c r="V7" s="93"/>
+      <c r="W7" s="93"/>
+      <c r="X7" s="93"/>
+      <c r="Y7" s="93"/>
+      <c r="Z7" s="93"/>
+      <c r="AA7" s="93"/>
+      <c r="AB7" s="94"/>
+      <c r="AC7" s="95"/>
+      <c r="AD7" s="96"/>
+      <c r="AE7" s="96"/>
+      <c r="AF7" s="96"/>
+      <c r="AG7" s="96"/>
+      <c r="AH7" s="96"/>
+      <c r="AI7" s="96"/>
+      <c r="AJ7" s="96"/>
+      <c r="AK7" s="96"/>
+      <c r="AL7" s="96"/>
+      <c r="AM7" s="96"/>
+      <c r="AN7" s="96"/>
+      <c r="AO7" s="96"/>
+      <c r="AP7" s="96"/>
+      <c r="AQ7" s="96"/>
+      <c r="AR7" s="96"/>
+      <c r="AS7" s="96"/>
+      <c r="AT7" s="96"/>
+      <c r="AU7" s="96"/>
+      <c r="AV7" s="97"/>
+      <c r="AW7" s="98"/>
+      <c r="AX7" s="99"/>
+      <c r="AY7" s="99"/>
+      <c r="AZ7" s="99"/>
+      <c r="BA7" s="99"/>
+      <c r="BB7" s="99"/>
+      <c r="BC7" s="99"/>
+      <c r="BD7" s="99"/>
+      <c r="BE7" s="99"/>
+      <c r="BF7" s="99"/>
+      <c r="BG7" s="99"/>
+      <c r="BH7" s="99"/>
+      <c r="BI7" s="99"/>
+      <c r="BJ7" s="99"/>
+      <c r="BK7" s="99"/>
+      <c r="BL7" s="99"/>
+      <c r="BM7" s="99"/>
+      <c r="BN7" s="99"/>
+      <c r="BO7" s="99"/>
+      <c r="BP7" s="100"/>
+      <c r="BQ7" s="101"/>
+      <c r="BR7" s="102"/>
+      <c r="BS7" s="102"/>
+      <c r="BT7" s="102"/>
+      <c r="BU7" s="102"/>
+      <c r="BV7" s="102"/>
+      <c r="BW7" s="102"/>
+      <c r="BX7" s="102"/>
+      <c r="BY7" s="102"/>
+      <c r="BZ7" s="102"/>
+      <c r="CA7" s="102"/>
+      <c r="CB7" s="102"/>
+      <c r="CC7" s="102"/>
+      <c r="CD7" s="102"/>
+      <c r="CE7" s="102"/>
+      <c r="CF7" s="102"/>
+      <c r="CG7" s="102"/>
+      <c r="CH7" s="102"/>
+      <c r="CI7" s="102"/>
+      <c r="CJ7" s="103"/>
       <c r="CK7" s="104" t="s">
         <v>52</v>
       </c>
@@ -2008,111 +2011,111 @@
       <c r="H8" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="87" t="s">
+      <c r="I8" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="87" t="s">
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="O8" s="88"/>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="88"/>
-      <c r="R8" s="88"/>
-      <c r="S8" s="87" t="s">
+      <c r="O8" s="84"/>
+      <c r="P8" s="84"/>
+      <c r="Q8" s="84"/>
+      <c r="R8" s="84"/>
+      <c r="S8" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="T8" s="88"/>
-      <c r="U8" s="88"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="88"/>
-      <c r="X8" s="87" t="s">
+      <c r="T8" s="84"/>
+      <c r="U8" s="84"/>
+      <c r="V8" s="84"/>
+      <c r="W8" s="84"/>
+      <c r="X8" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="Y8" s="88"/>
-      <c r="Z8" s="88"/>
-      <c r="AA8" s="88"/>
-      <c r="AB8" s="88"/>
-      <c r="AC8" s="92" t="s">
+      <c r="Y8" s="84"/>
+      <c r="Z8" s="84"/>
+      <c r="AA8" s="84"/>
+      <c r="AB8" s="84"/>
+      <c r="AC8" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="AD8" s="93"/>
-      <c r="AE8" s="93"/>
-      <c r="AF8" s="93"/>
-      <c r="AG8" s="93"/>
-      <c r="AH8" s="92" t="s">
+      <c r="AD8" s="86"/>
+      <c r="AE8" s="86"/>
+      <c r="AF8" s="86"/>
+      <c r="AG8" s="86"/>
+      <c r="AH8" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="AI8" s="93"/>
-      <c r="AJ8" s="93"/>
-      <c r="AK8" s="93"/>
-      <c r="AL8" s="93"/>
-      <c r="AM8" s="92" t="s">
+      <c r="AI8" s="86"/>
+      <c r="AJ8" s="86"/>
+      <c r="AK8" s="86"/>
+      <c r="AL8" s="86"/>
+      <c r="AM8" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="AN8" s="93"/>
-      <c r="AO8" s="93"/>
-      <c r="AP8" s="93"/>
-      <c r="AQ8" s="93"/>
-      <c r="AR8" s="92" t="s">
+      <c r="AN8" s="86"/>
+      <c r="AO8" s="86"/>
+      <c r="AP8" s="86"/>
+      <c r="AQ8" s="86"/>
+      <c r="AR8" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="AS8" s="93"/>
-      <c r="AT8" s="93"/>
-      <c r="AU8" s="93"/>
-      <c r="AV8" s="93"/>
-      <c r="AW8" s="97" t="s">
+      <c r="AS8" s="86"/>
+      <c r="AT8" s="86"/>
+      <c r="AU8" s="86"/>
+      <c r="AV8" s="86"/>
+      <c r="AW8" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="AX8" s="98"/>
-      <c r="AY8" s="98"/>
-      <c r="AZ8" s="98"/>
-      <c r="BA8" s="98"/>
-      <c r="BB8" s="97" t="s">
+      <c r="AX8" s="88"/>
+      <c r="AY8" s="88"/>
+      <c r="AZ8" s="88"/>
+      <c r="BA8" s="88"/>
+      <c r="BB8" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="BC8" s="98"/>
-      <c r="BD8" s="98"/>
-      <c r="BE8" s="98"/>
-      <c r="BF8" s="98"/>
-      <c r="BG8" s="97" t="s">
+      <c r="BC8" s="88"/>
+      <c r="BD8" s="88"/>
+      <c r="BE8" s="88"/>
+      <c r="BF8" s="88"/>
+      <c r="BG8" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="BH8" s="98"/>
-      <c r="BI8" s="98"/>
-      <c r="BJ8" s="98"/>
-      <c r="BK8" s="98"/>
-      <c r="BL8" s="97" t="s">
+      <c r="BH8" s="88"/>
+      <c r="BI8" s="88"/>
+      <c r="BJ8" s="88"/>
+      <c r="BK8" s="88"/>
+      <c r="BL8" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="BM8" s="98"/>
-      <c r="BN8" s="98"/>
-      <c r="BO8" s="98"/>
-      <c r="BP8" s="98"/>
-      <c r="BQ8" s="102" t="s">
+      <c r="BM8" s="88"/>
+      <c r="BN8" s="88"/>
+      <c r="BO8" s="88"/>
+      <c r="BP8" s="88"/>
+      <c r="BQ8" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="BR8" s="103"/>
-      <c r="BS8" s="103"/>
-      <c r="BT8" s="103"/>
-      <c r="BU8" s="103"/>
-      <c r="BV8" s="102" t="s">
+      <c r="BR8" s="82"/>
+      <c r="BS8" s="82"/>
+      <c r="BT8" s="82"/>
+      <c r="BU8" s="82"/>
+      <c r="BV8" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="BW8" s="103"/>
-      <c r="BX8" s="103"/>
-      <c r="BY8" s="103"/>
-      <c r="BZ8" s="103"/>
-      <c r="CA8" s="102" t="s">
+      <c r="BW8" s="82"/>
+      <c r="BX8" s="82"/>
+      <c r="BY8" s="82"/>
+      <c r="BZ8" s="82"/>
+      <c r="CA8" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="CB8" s="103"/>
-      <c r="CC8" s="103"/>
-      <c r="CD8" s="103"/>
-      <c r="CE8" s="103"/>
+      <c r="CB8" s="82"/>
+      <c r="CC8" s="82"/>
+      <c r="CD8" s="82"/>
+      <c r="CE8" s="82"/>
       <c r="CF8" s="106" t="s">
         <v>50</v>
       </c>
@@ -2120,13 +2123,13 @@
       <c r="CH8" s="107"/>
       <c r="CI8" s="107"/>
       <c r="CJ8" s="108"/>
-      <c r="CK8" s="81" t="s">
+      <c r="CK8" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="CL8" s="82"/>
-      <c r="CM8" s="82"/>
-      <c r="CN8" s="82"/>
-      <c r="CO8" s="83"/>
+      <c r="CL8" s="90"/>
+      <c r="CM8" s="90"/>
+      <c r="CN8" s="90"/>
+      <c r="CO8" s="91"/>
       <c r="CP8" s="57"/>
     </row>
     <row r="9" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6349,13 +6352,8 @@
       <c r="C45" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="D1:D45" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <mergeCells count="22">
-    <mergeCell ref="BV8:BZ8"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="AC8:AG8"/>
-    <mergeCell ref="AH8:AL8"/>
-    <mergeCell ref="AR8:AV8"/>
-    <mergeCell ref="AW8:BA8"/>
     <mergeCell ref="CK8:CO8"/>
     <mergeCell ref="I7:AB7"/>
     <mergeCell ref="X8:AB8"/>
@@ -6372,6 +6370,12 @@
     <mergeCell ref="BB8:BF8"/>
     <mergeCell ref="BL8:BP8"/>
     <mergeCell ref="BQ8:BU8"/>
+    <mergeCell ref="BV8:BZ8"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="AC8:AG8"/>
+    <mergeCell ref="AH8:AL8"/>
+    <mergeCell ref="AR8:AV8"/>
+    <mergeCell ref="AW8:BA8"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="D37:G37">

--- a/FASE 1/Evidencias Grupales/Gantt CAPSTONE - SISTEMA DE GESTION PARA TRANSPORTE DE PASAJEROS.xlsx
+++ b/FASE 1/Evidencias Grupales/Gantt CAPSTONE - SISTEMA DE GESTION PARA TRANSPORTE DE PASAJEROS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\capstone-2026\FASE 1\Evidencias Grupales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500733D6-3ECF-4E6A-B5DE-32ADB553163D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2BBAF3-8469-4106-BB81-3447D2DDB3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gestión Proyecto Carta Gantt" sheetId="3" r:id="rId1"/>
@@ -501,7 +501,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1515,73 +1515,73 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1825,7 +1825,7 @@
     <tabColor theme="3" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="B1:CP45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="14.625" customWidth="1"/>
@@ -1839,7 +1839,7 @@
     <col min="94" max="94" width="2.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:94" s="34" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:94" s="34" customFormat="1" ht="50.1" customHeight="1">
       <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
@@ -1861,7 +1861,7 @@
       <c r="R1" s="36"/>
       <c r="S1" s="36"/>
     </row>
-    <row r="2" spans="2:94" s="1" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:94" s="1" customFormat="1" ht="35.1" customHeight="1">
       <c r="B2" s="44" t="s">
         <v>1</v>
       </c>
@@ -1869,19 +1869,19 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="2:94" s="1" customFormat="1" ht="27.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:94" s="1" customFormat="1" ht="27.75" thickBot="1">
       <c r="B3" s="47" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="48"/>
     </row>
-    <row r="4" spans="2:94" s="1" customFormat="1" ht="27.75" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:94" s="1" customFormat="1" ht="27.75" thickTop="1">
       <c r="B4" s="46" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="43"/>
     </row>
-    <row r="5" spans="2:94" s="1" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:94" s="1" customFormat="1" ht="17.25">
       <c r="B5" s="45" t="s">
         <v>4</v>
       </c>
@@ -1889,10 +1889,10 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="6" spans="2:94" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:94" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1900,86 +1900,86 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="93"/>
-      <c r="P7" s="93"/>
-      <c r="Q7" s="93"/>
-      <c r="R7" s="93"/>
-      <c r="S7" s="93"/>
-      <c r="T7" s="93"/>
-      <c r="U7" s="93"/>
-      <c r="V7" s="93"/>
-      <c r="W7" s="93"/>
-      <c r="X7" s="93"/>
-      <c r="Y7" s="93"/>
-      <c r="Z7" s="93"/>
-      <c r="AA7" s="93"/>
-      <c r="AB7" s="94"/>
-      <c r="AC7" s="95"/>
-      <c r="AD7" s="96"/>
-      <c r="AE7" s="96"/>
-      <c r="AF7" s="96"/>
-      <c r="AG7" s="96"/>
-      <c r="AH7" s="96"/>
-      <c r="AI7" s="96"/>
-      <c r="AJ7" s="96"/>
-      <c r="AK7" s="96"/>
-      <c r="AL7" s="96"/>
-      <c r="AM7" s="96"/>
-      <c r="AN7" s="96"/>
-      <c r="AO7" s="96"/>
-      <c r="AP7" s="96"/>
-      <c r="AQ7" s="96"/>
-      <c r="AR7" s="96"/>
-      <c r="AS7" s="96"/>
-      <c r="AT7" s="96"/>
-      <c r="AU7" s="96"/>
-      <c r="AV7" s="97"/>
-      <c r="AW7" s="98"/>
-      <c r="AX7" s="99"/>
-      <c r="AY7" s="99"/>
-      <c r="AZ7" s="99"/>
-      <c r="BA7" s="99"/>
-      <c r="BB7" s="99"/>
-      <c r="BC7" s="99"/>
-      <c r="BD7" s="99"/>
-      <c r="BE7" s="99"/>
-      <c r="BF7" s="99"/>
-      <c r="BG7" s="99"/>
-      <c r="BH7" s="99"/>
-      <c r="BI7" s="99"/>
-      <c r="BJ7" s="99"/>
-      <c r="BK7" s="99"/>
-      <c r="BL7" s="99"/>
-      <c r="BM7" s="99"/>
-      <c r="BN7" s="99"/>
-      <c r="BO7" s="99"/>
-      <c r="BP7" s="100"/>
-      <c r="BQ7" s="101"/>
-      <c r="BR7" s="102"/>
-      <c r="BS7" s="102"/>
-      <c r="BT7" s="102"/>
-      <c r="BU7" s="102"/>
-      <c r="BV7" s="102"/>
-      <c r="BW7" s="102"/>
-      <c r="BX7" s="102"/>
-      <c r="BY7" s="102"/>
-      <c r="BZ7" s="102"/>
-      <c r="CA7" s="102"/>
-      <c r="CB7" s="102"/>
-      <c r="CC7" s="102"/>
-      <c r="CD7" s="102"/>
-      <c r="CE7" s="102"/>
-      <c r="CF7" s="102"/>
-      <c r="CG7" s="102"/>
-      <c r="CH7" s="102"/>
-      <c r="CI7" s="102"/>
-      <c r="CJ7" s="103"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="85"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="85"/>
+      <c r="R7" s="85"/>
+      <c r="S7" s="85"/>
+      <c r="T7" s="85"/>
+      <c r="U7" s="85"/>
+      <c r="V7" s="85"/>
+      <c r="W7" s="85"/>
+      <c r="X7" s="85"/>
+      <c r="Y7" s="85"/>
+      <c r="Z7" s="85"/>
+      <c r="AA7" s="85"/>
+      <c r="AB7" s="86"/>
+      <c r="AC7" s="89"/>
+      <c r="AD7" s="90"/>
+      <c r="AE7" s="90"/>
+      <c r="AF7" s="90"/>
+      <c r="AG7" s="90"/>
+      <c r="AH7" s="90"/>
+      <c r="AI7" s="90"/>
+      <c r="AJ7" s="90"/>
+      <c r="AK7" s="90"/>
+      <c r="AL7" s="90"/>
+      <c r="AM7" s="90"/>
+      <c r="AN7" s="90"/>
+      <c r="AO7" s="90"/>
+      <c r="AP7" s="90"/>
+      <c r="AQ7" s="90"/>
+      <c r="AR7" s="90"/>
+      <c r="AS7" s="90"/>
+      <c r="AT7" s="90"/>
+      <c r="AU7" s="90"/>
+      <c r="AV7" s="91"/>
+      <c r="AW7" s="94"/>
+      <c r="AX7" s="95"/>
+      <c r="AY7" s="95"/>
+      <c r="AZ7" s="95"/>
+      <c r="BA7" s="95"/>
+      <c r="BB7" s="95"/>
+      <c r="BC7" s="95"/>
+      <c r="BD7" s="95"/>
+      <c r="BE7" s="95"/>
+      <c r="BF7" s="95"/>
+      <c r="BG7" s="95"/>
+      <c r="BH7" s="95"/>
+      <c r="BI7" s="95"/>
+      <c r="BJ7" s="95"/>
+      <c r="BK7" s="95"/>
+      <c r="BL7" s="95"/>
+      <c r="BM7" s="95"/>
+      <c r="BN7" s="95"/>
+      <c r="BO7" s="95"/>
+      <c r="BP7" s="96"/>
+      <c r="BQ7" s="99"/>
+      <c r="BR7" s="100"/>
+      <c r="BS7" s="100"/>
+      <c r="BT7" s="100"/>
+      <c r="BU7" s="100"/>
+      <c r="BV7" s="100"/>
+      <c r="BW7" s="100"/>
+      <c r="BX7" s="100"/>
+      <c r="BY7" s="100"/>
+      <c r="BZ7" s="100"/>
+      <c r="CA7" s="100"/>
+      <c r="CB7" s="100"/>
+      <c r="CC7" s="100"/>
+      <c r="CD7" s="100"/>
+      <c r="CE7" s="100"/>
+      <c r="CF7" s="100"/>
+      <c r="CG7" s="100"/>
+      <c r="CH7" s="100"/>
+      <c r="CI7" s="100"/>
+      <c r="CJ7" s="101"/>
       <c r="CK7" s="104" t="s">
         <v>52</v>
       </c>
@@ -1989,7 +1989,7 @@
       <c r="CO7" s="105"/>
       <c r="CP7" s="56"/>
     </row>
-    <row r="8" spans="2:94" ht="27" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:94" ht="27">
       <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
@@ -2011,111 +2011,111 @@
       <c r="H8" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="83" t="s">
+      <c r="I8" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="84"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="84"/>
-      <c r="M8" s="84"/>
-      <c r="N8" s="83" t="s">
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="O8" s="84"/>
-      <c r="P8" s="84"/>
-      <c r="Q8" s="84"/>
-      <c r="R8" s="84"/>
-      <c r="S8" s="83" t="s">
+      <c r="O8" s="88"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
+      <c r="R8" s="88"/>
+      <c r="S8" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="T8" s="84"/>
-      <c r="U8" s="84"/>
-      <c r="V8" s="84"/>
-      <c r="W8" s="84"/>
-      <c r="X8" s="83" t="s">
+      <c r="T8" s="88"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="Y8" s="84"/>
-      <c r="Z8" s="84"/>
-      <c r="AA8" s="84"/>
-      <c r="AB8" s="84"/>
-      <c r="AC8" s="85" t="s">
+      <c r="Y8" s="88"/>
+      <c r="Z8" s="88"/>
+      <c r="AA8" s="88"/>
+      <c r="AB8" s="88"/>
+      <c r="AC8" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="AD8" s="86"/>
-      <c r="AE8" s="86"/>
-      <c r="AF8" s="86"/>
-      <c r="AG8" s="86"/>
-      <c r="AH8" s="85" t="s">
+      <c r="AD8" s="93"/>
+      <c r="AE8" s="93"/>
+      <c r="AF8" s="93"/>
+      <c r="AG8" s="93"/>
+      <c r="AH8" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="AI8" s="86"/>
-      <c r="AJ8" s="86"/>
-      <c r="AK8" s="86"/>
-      <c r="AL8" s="86"/>
-      <c r="AM8" s="85" t="s">
+      <c r="AI8" s="93"/>
+      <c r="AJ8" s="93"/>
+      <c r="AK8" s="93"/>
+      <c r="AL8" s="93"/>
+      <c r="AM8" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="AN8" s="86"/>
-      <c r="AO8" s="86"/>
-      <c r="AP8" s="86"/>
-      <c r="AQ8" s="86"/>
-      <c r="AR8" s="85" t="s">
+      <c r="AN8" s="93"/>
+      <c r="AO8" s="93"/>
+      <c r="AP8" s="93"/>
+      <c r="AQ8" s="93"/>
+      <c r="AR8" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="AS8" s="86"/>
-      <c r="AT8" s="86"/>
-      <c r="AU8" s="86"/>
-      <c r="AV8" s="86"/>
-      <c r="AW8" s="87" t="s">
+      <c r="AS8" s="93"/>
+      <c r="AT8" s="93"/>
+      <c r="AU8" s="93"/>
+      <c r="AV8" s="93"/>
+      <c r="AW8" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="AX8" s="88"/>
-      <c r="AY8" s="88"/>
-      <c r="AZ8" s="88"/>
-      <c r="BA8" s="88"/>
-      <c r="BB8" s="87" t="s">
+      <c r="AX8" s="98"/>
+      <c r="AY8" s="98"/>
+      <c r="AZ8" s="98"/>
+      <c r="BA8" s="98"/>
+      <c r="BB8" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="BC8" s="88"/>
-      <c r="BD8" s="88"/>
-      <c r="BE8" s="88"/>
-      <c r="BF8" s="88"/>
-      <c r="BG8" s="87" t="s">
+      <c r="BC8" s="98"/>
+      <c r="BD8" s="98"/>
+      <c r="BE8" s="98"/>
+      <c r="BF8" s="98"/>
+      <c r="BG8" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="BH8" s="88"/>
-      <c r="BI8" s="88"/>
-      <c r="BJ8" s="88"/>
-      <c r="BK8" s="88"/>
-      <c r="BL8" s="87" t="s">
+      <c r="BH8" s="98"/>
+      <c r="BI8" s="98"/>
+      <c r="BJ8" s="98"/>
+      <c r="BK8" s="98"/>
+      <c r="BL8" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="BM8" s="88"/>
-      <c r="BN8" s="88"/>
-      <c r="BO8" s="88"/>
-      <c r="BP8" s="88"/>
-      <c r="BQ8" s="81" t="s">
+      <c r="BM8" s="98"/>
+      <c r="BN8" s="98"/>
+      <c r="BO8" s="98"/>
+      <c r="BP8" s="98"/>
+      <c r="BQ8" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="BR8" s="82"/>
-      <c r="BS8" s="82"/>
-      <c r="BT8" s="82"/>
-      <c r="BU8" s="82"/>
-      <c r="BV8" s="81" t="s">
+      <c r="BR8" s="103"/>
+      <c r="BS8" s="103"/>
+      <c r="BT8" s="103"/>
+      <c r="BU8" s="103"/>
+      <c r="BV8" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="BW8" s="82"/>
-      <c r="BX8" s="82"/>
-      <c r="BY8" s="82"/>
-      <c r="BZ8" s="82"/>
-      <c r="CA8" s="81" t="s">
+      <c r="BW8" s="103"/>
+      <c r="BX8" s="103"/>
+      <c r="BY8" s="103"/>
+      <c r="BZ8" s="103"/>
+      <c r="CA8" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="CB8" s="82"/>
-      <c r="CC8" s="82"/>
-      <c r="CD8" s="82"/>
-      <c r="CE8" s="82"/>
+      <c r="CB8" s="103"/>
+      <c r="CC8" s="103"/>
+      <c r="CD8" s="103"/>
+      <c r="CE8" s="103"/>
       <c r="CF8" s="106" t="s">
         <v>50</v>
       </c>
@@ -2123,16 +2123,16 @@
       <c r="CH8" s="107"/>
       <c r="CI8" s="107"/>
       <c r="CJ8" s="108"/>
-      <c r="CK8" s="89" t="s">
+      <c r="CK8" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="CL8" s="90"/>
-      <c r="CM8" s="90"/>
-      <c r="CN8" s="90"/>
-      <c r="CO8" s="91"/>
+      <c r="CL8" s="82"/>
+      <c r="CM8" s="82"/>
+      <c r="CN8" s="82"/>
+      <c r="CO8" s="83"/>
       <c r="CP8" s="57"/>
     </row>
-    <row r="9" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B9" s="9" t="s">
         <v>6</v>
       </c>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="CP9" s="54"/>
     </row>
-    <row r="10" spans="2:94" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:94" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" thickTop="1">
       <c r="B10" s="61" t="s">
         <v>147</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="CO10" s="58"/>
       <c r="CP10" s="59"/>
     </row>
-    <row r="11" spans="2:94" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:94" ht="19.5" customHeight="1">
       <c r="B11" s="62" t="s">
         <v>17</v>
       </c>
@@ -2660,7 +2660,7 @@
       <c r="CO11" s="21"/>
       <c r="CP11" s="20"/>
     </row>
-    <row r="12" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B12" s="62" t="s">
         <v>18</v>
       </c>
@@ -2777,7 +2777,7 @@
       <c r="CO12" s="21"/>
       <c r="CP12" s="20"/>
     </row>
-    <row r="13" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B13" s="62" t="s">
         <v>19</v>
       </c>
@@ -2894,7 +2894,7 @@
       <c r="CO13" s="21"/>
       <c r="CP13" s="20"/>
     </row>
-    <row r="14" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B14" s="62" t="s">
         <v>20</v>
       </c>
@@ -3013,7 +3013,7 @@
       <c r="CO14" s="21"/>
       <c r="CP14" s="20"/>
     </row>
-    <row r="15" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="62" t="s">
         <v>21</v>
       </c>
@@ -3140,7 +3140,7 @@
       <c r="CO15" s="21"/>
       <c r="CP15" s="20"/>
     </row>
-    <row r="16" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B16" s="62" t="s">
         <v>22</v>
       </c>
@@ -3257,7 +3257,7 @@
       <c r="CO16" s="21"/>
       <c r="CP16" s="20"/>
     </row>
-    <row r="17" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="62" t="s">
         <v>73</v>
       </c>
@@ -3368,7 +3368,7 @@
       <c r="CO17" s="21"/>
       <c r="CP17" s="20"/>
     </row>
-    <row r="18" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="62">
         <v>2</v>
       </c>
@@ -3580,7 +3580,7 @@
       <c r="CO18" s="19"/>
       <c r="CP18" s="59"/>
     </row>
-    <row r="19" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="62" t="s">
         <v>23</v>
       </c>
@@ -3695,7 +3695,7 @@
       <c r="CO19" s="21"/>
       <c r="CP19" s="20"/>
     </row>
-    <row r="20" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="62" t="s">
         <v>24</v>
       </c>
@@ -3812,7 +3812,7 @@
       <c r="CO20" s="21"/>
       <c r="CP20" s="20"/>
     </row>
-    <row r="21" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="62" t="s">
         <v>25</v>
       </c>
@@ -3929,7 +3929,7 @@
       <c r="CO21" s="21"/>
       <c r="CP21" s="20"/>
     </row>
-    <row r="22" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B22" s="62" t="s">
         <v>26</v>
       </c>
@@ -4046,7 +4046,7 @@
       <c r="CO22" s="21"/>
       <c r="CP22" s="20"/>
     </row>
-    <row r="23" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="62" t="s">
         <v>90</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>93</v>
       </c>
       <c r="H23" s="69">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I23" s="38"/>
       <c r="J23" s="21"/>
@@ -4185,7 +4185,7 @@
       <c r="CO23" s="21"/>
       <c r="CP23" s="20"/>
     </row>
-    <row r="24" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="62" t="s">
         <v>94</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>98</v>
       </c>
       <c r="H24" s="69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="38"/>
       <c r="J24" s="21"/>
@@ -4314,7 +4314,7 @@
       <c r="CO24" s="21"/>
       <c r="CP24" s="20"/>
     </row>
-    <row r="25" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B25" s="62" t="s">
         <v>99</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>98</v>
       </c>
       <c r="H25" s="69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="38"/>
       <c r="J25" s="21"/>
@@ -4443,7 +4443,7 @@
       <c r="CO25" s="21"/>
       <c r="CP25" s="20"/>
     </row>
-    <row r="26" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B26" s="62" t="s">
         <v>101</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>98</v>
       </c>
       <c r="H26" s="69">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I26" s="38"/>
       <c r="J26" s="21"/>
@@ -4572,7 +4572,7 @@
       <c r="CO26" s="21"/>
       <c r="CP26" s="20"/>
     </row>
-    <row r="27" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B27" s="62" t="s">
         <v>103</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>98</v>
       </c>
       <c r="H27" s="69">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I27" s="38"/>
       <c r="J27" s="21"/>
@@ -4701,7 +4701,7 @@
       <c r="CO27" s="21"/>
       <c r="CP27" s="20"/>
     </row>
-    <row r="28" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B28" s="62" t="s">
         <v>105</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>67</v>
       </c>
       <c r="H28" s="69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="38"/>
       <c r="J28" s="21"/>
@@ -4820,7 +4820,7 @@
       <c r="CO28" s="21"/>
       <c r="CP28" s="20"/>
     </row>
-    <row r="29" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B29" s="62" t="s">
         <v>109</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>63</v>
       </c>
       <c r="H29" s="69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="38"/>
       <c r="J29" s="21"/>
@@ -4937,7 +4937,7 @@
       <c r="CO29" s="21"/>
       <c r="CP29" s="20"/>
     </row>
-    <row r="30" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B30" s="62" t="s">
         <v>112</v>
       </c>
@@ -4957,7 +4957,7 @@
         <v>63</v>
       </c>
       <c r="H30" s="69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="38"/>
       <c r="J30" s="21"/>
@@ -5054,7 +5054,7 @@
       <c r="CO30" s="21"/>
       <c r="CP30" s="20"/>
     </row>
-    <row r="31" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B31" s="62" t="s">
         <v>114</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>118</v>
       </c>
       <c r="H31" s="69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="38"/>
       <c r="J31" s="21"/>
@@ -5180,7 +5180,7 @@
       <c r="CO31" s="21"/>
       <c r="CP31" s="20"/>
     </row>
-    <row r="32" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B32" s="62" t="s">
         <v>119</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>123</v>
       </c>
       <c r="H32" s="69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="38"/>
       <c r="J32" s="21"/>
@@ -5303,7 +5303,7 @@
       <c r="CO32" s="21"/>
       <c r="CP32" s="20"/>
     </row>
-    <row r="33" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B33" s="62" t="s">
         <v>124</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>59</v>
       </c>
       <c r="H33" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="38"/>
       <c r="J33" s="21"/>
@@ -5418,7 +5418,7 @@
       <c r="CO33" s="21"/>
       <c r="CP33" s="20"/>
     </row>
-    <row r="34" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B34" s="62" t="s">
         <v>128</v>
       </c>
@@ -5437,8 +5437,8 @@
       <c r="G34" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="H34" s="69">
-        <v>0</v>
+      <c r="H34" s="70">
+        <v>1</v>
       </c>
       <c r="I34" s="38"/>
       <c r="J34" s="21"/>
@@ -5529,7 +5529,7 @@
       <c r="CO34" s="21"/>
       <c r="CP34" s="20"/>
     </row>
-    <row r="35" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B35" s="62" t="s">
         <v>130</v>
       </c>
@@ -5642,7 +5642,7 @@
       <c r="CO35" s="21"/>
       <c r="CP35" s="20"/>
     </row>
-    <row r="36" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B36" s="62" t="s">
         <v>134</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="CO36" s="21"/>
       <c r="CP36" s="20"/>
     </row>
-    <row r="37" spans="2:94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:94" ht="20.100000000000001" customHeight="1">
       <c r="B37" s="62">
         <v>3</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="B38" s="62" t="s">
         <v>27</v>
       </c>
@@ -6001,7 +6001,7 @@
       <c r="CO38" s="26"/>
       <c r="CP38" s="25"/>
     </row>
-    <row r="39" spans="2:94" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:94" ht="16.5">
       <c r="B39" s="62" t="s">
         <v>28</v>
       </c>
@@ -6120,7 +6120,7 @@
       <c r="CO39" s="21"/>
       <c r="CP39" s="20"/>
     </row>
-    <row r="40" spans="2:94" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:94" ht="16.5">
       <c r="B40" s="62" t="s">
         <v>29</v>
       </c>
@@ -6237,7 +6237,7 @@
       <c r="CO40" s="21"/>
       <c r="CP40" s="20"/>
     </row>
-    <row r="41" spans="2:94" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:94" ht="16.5">
       <c r="B41" s="62" t="s">
         <v>145</v>
       </c>
@@ -6348,12 +6348,18 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="2:94" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:94" ht="19.5">
       <c r="C45" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="D1:D45" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <mergeCells count="22">
+    <mergeCell ref="BV8:BZ8"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="AC8:AG8"/>
+    <mergeCell ref="AH8:AL8"/>
+    <mergeCell ref="AR8:AV8"/>
+    <mergeCell ref="AW8:BA8"/>
     <mergeCell ref="CK8:CO8"/>
     <mergeCell ref="I7:AB7"/>
     <mergeCell ref="X8:AB8"/>
@@ -6370,12 +6376,6 @@
     <mergeCell ref="BB8:BF8"/>
     <mergeCell ref="BL8:BP8"/>
     <mergeCell ref="BQ8:BU8"/>
-    <mergeCell ref="BV8:BZ8"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="AC8:AG8"/>
-    <mergeCell ref="AH8:AL8"/>
-    <mergeCell ref="AR8:AV8"/>
-    <mergeCell ref="AW8:BA8"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="D37:G37">

--- a/FASE 1/Evidencias Grupales/Gantt CAPSTONE - SISTEMA DE GESTION PARA TRANSPORTE DE PASAJEROS.xlsx
+++ b/FASE 1/Evidencias Grupales/Gantt CAPSTONE - SISTEMA DE GESTION PARA TRANSPORTE DE PASAJEROS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\capstone-2026\FASE 1\Evidencias Grupales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2BBAF3-8469-4106-BB81-3447D2DDB3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1829FB13-6D7F-45BA-84F0-ADE657B60253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gestión Proyecto Carta Gantt" sheetId="3" r:id="rId1"/>
@@ -1515,6 +1515,30 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1533,12 +1557,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1548,12 +1566,6 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1563,12 +1575,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1576,12 +1582,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1900,86 +1900,86 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="85"/>
-      <c r="L7" s="85"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="85"/>
-      <c r="Q7" s="85"/>
-      <c r="R7" s="85"/>
-      <c r="S7" s="85"/>
-      <c r="T7" s="85"/>
-      <c r="U7" s="85"/>
-      <c r="V7" s="85"/>
-      <c r="W7" s="85"/>
-      <c r="X7" s="85"/>
-      <c r="Y7" s="85"/>
-      <c r="Z7" s="85"/>
-      <c r="AA7" s="85"/>
-      <c r="AB7" s="86"/>
-      <c r="AC7" s="89"/>
-      <c r="AD7" s="90"/>
-      <c r="AE7" s="90"/>
-      <c r="AF7" s="90"/>
-      <c r="AG7" s="90"/>
-      <c r="AH7" s="90"/>
-      <c r="AI7" s="90"/>
-      <c r="AJ7" s="90"/>
-      <c r="AK7" s="90"/>
-      <c r="AL7" s="90"/>
-      <c r="AM7" s="90"/>
-      <c r="AN7" s="90"/>
-      <c r="AO7" s="90"/>
-      <c r="AP7" s="90"/>
-      <c r="AQ7" s="90"/>
-      <c r="AR7" s="90"/>
-      <c r="AS7" s="90"/>
-      <c r="AT7" s="90"/>
-      <c r="AU7" s="90"/>
-      <c r="AV7" s="91"/>
-      <c r="AW7" s="94"/>
-      <c r="AX7" s="95"/>
-      <c r="AY7" s="95"/>
-      <c r="AZ7" s="95"/>
-      <c r="BA7" s="95"/>
-      <c r="BB7" s="95"/>
-      <c r="BC7" s="95"/>
-      <c r="BD7" s="95"/>
-      <c r="BE7" s="95"/>
-      <c r="BF7" s="95"/>
-      <c r="BG7" s="95"/>
-      <c r="BH7" s="95"/>
-      <c r="BI7" s="95"/>
-      <c r="BJ7" s="95"/>
-      <c r="BK7" s="95"/>
-      <c r="BL7" s="95"/>
-      <c r="BM7" s="95"/>
-      <c r="BN7" s="95"/>
-      <c r="BO7" s="95"/>
-      <c r="BP7" s="96"/>
-      <c r="BQ7" s="99"/>
-      <c r="BR7" s="100"/>
-      <c r="BS7" s="100"/>
-      <c r="BT7" s="100"/>
-      <c r="BU7" s="100"/>
-      <c r="BV7" s="100"/>
-      <c r="BW7" s="100"/>
-      <c r="BX7" s="100"/>
-      <c r="BY7" s="100"/>
-      <c r="BZ7" s="100"/>
-      <c r="CA7" s="100"/>
-      <c r="CB7" s="100"/>
-      <c r="CC7" s="100"/>
-      <c r="CD7" s="100"/>
-      <c r="CE7" s="100"/>
-      <c r="CF7" s="100"/>
-      <c r="CG7" s="100"/>
-      <c r="CH7" s="100"/>
-      <c r="CI7" s="100"/>
-      <c r="CJ7" s="101"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="93"/>
+      <c r="P7" s="93"/>
+      <c r="Q7" s="93"/>
+      <c r="R7" s="93"/>
+      <c r="S7" s="93"/>
+      <c r="T7" s="93"/>
+      <c r="U7" s="93"/>
+      <c r="V7" s="93"/>
+      <c r="W7" s="93"/>
+      <c r="X7" s="93"/>
+      <c r="Y7" s="93"/>
+      <c r="Z7" s="93"/>
+      <c r="AA7" s="93"/>
+      <c r="AB7" s="94"/>
+      <c r="AC7" s="95"/>
+      <c r="AD7" s="96"/>
+      <c r="AE7" s="96"/>
+      <c r="AF7" s="96"/>
+      <c r="AG7" s="96"/>
+      <c r="AH7" s="96"/>
+      <c r="AI7" s="96"/>
+      <c r="AJ7" s="96"/>
+      <c r="AK7" s="96"/>
+      <c r="AL7" s="96"/>
+      <c r="AM7" s="96"/>
+      <c r="AN7" s="96"/>
+      <c r="AO7" s="96"/>
+      <c r="AP7" s="96"/>
+      <c r="AQ7" s="96"/>
+      <c r="AR7" s="96"/>
+      <c r="AS7" s="96"/>
+      <c r="AT7" s="96"/>
+      <c r="AU7" s="96"/>
+      <c r="AV7" s="97"/>
+      <c r="AW7" s="98"/>
+      <c r="AX7" s="99"/>
+      <c r="AY7" s="99"/>
+      <c r="AZ7" s="99"/>
+      <c r="BA7" s="99"/>
+      <c r="BB7" s="99"/>
+      <c r="BC7" s="99"/>
+      <c r="BD7" s="99"/>
+      <c r="BE7" s="99"/>
+      <c r="BF7" s="99"/>
+      <c r="BG7" s="99"/>
+      <c r="BH7" s="99"/>
+      <c r="BI7" s="99"/>
+      <c r="BJ7" s="99"/>
+      <c r="BK7" s="99"/>
+      <c r="BL7" s="99"/>
+      <c r="BM7" s="99"/>
+      <c r="BN7" s="99"/>
+      <c r="BO7" s="99"/>
+      <c r="BP7" s="100"/>
+      <c r="BQ7" s="101"/>
+      <c r="BR7" s="102"/>
+      <c r="BS7" s="102"/>
+      <c r="BT7" s="102"/>
+      <c r="BU7" s="102"/>
+      <c r="BV7" s="102"/>
+      <c r="BW7" s="102"/>
+      <c r="BX7" s="102"/>
+      <c r="BY7" s="102"/>
+      <c r="BZ7" s="102"/>
+      <c r="CA7" s="102"/>
+      <c r="CB7" s="102"/>
+      <c r="CC7" s="102"/>
+      <c r="CD7" s="102"/>
+      <c r="CE7" s="102"/>
+      <c r="CF7" s="102"/>
+      <c r="CG7" s="102"/>
+      <c r="CH7" s="102"/>
+      <c r="CI7" s="102"/>
+      <c r="CJ7" s="103"/>
       <c r="CK7" s="104" t="s">
         <v>52</v>
       </c>
@@ -2011,111 +2011,111 @@
       <c r="H8" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="87" t="s">
+      <c r="I8" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="87" t="s">
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="O8" s="88"/>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="88"/>
-      <c r="R8" s="88"/>
-      <c r="S8" s="87" t="s">
+      <c r="O8" s="84"/>
+      <c r="P8" s="84"/>
+      <c r="Q8" s="84"/>
+      <c r="R8" s="84"/>
+      <c r="S8" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="T8" s="88"/>
-      <c r="U8" s="88"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="88"/>
-      <c r="X8" s="87" t="s">
+      <c r="T8" s="84"/>
+      <c r="U8" s="84"/>
+      <c r="V8" s="84"/>
+      <c r="W8" s="84"/>
+      <c r="X8" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="Y8" s="88"/>
-      <c r="Z8" s="88"/>
-      <c r="AA8" s="88"/>
-      <c r="AB8" s="88"/>
-      <c r="AC8" s="92" t="s">
+      <c r="Y8" s="84"/>
+      <c r="Z8" s="84"/>
+      <c r="AA8" s="84"/>
+      <c r="AB8" s="84"/>
+      <c r="AC8" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="AD8" s="93"/>
-      <c r="AE8" s="93"/>
-      <c r="AF8" s="93"/>
-      <c r="AG8" s="93"/>
-      <c r="AH8" s="92" t="s">
+      <c r="AD8" s="86"/>
+      <c r="AE8" s="86"/>
+      <c r="AF8" s="86"/>
+      <c r="AG8" s="86"/>
+      <c r="AH8" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="AI8" s="93"/>
-      <c r="AJ8" s="93"/>
-      <c r="AK8" s="93"/>
-      <c r="AL8" s="93"/>
-      <c r="AM8" s="92" t="s">
+      <c r="AI8" s="86"/>
+      <c r="AJ8" s="86"/>
+      <c r="AK8" s="86"/>
+      <c r="AL8" s="86"/>
+      <c r="AM8" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="AN8" s="93"/>
-      <c r="AO8" s="93"/>
-      <c r="AP8" s="93"/>
-      <c r="AQ8" s="93"/>
-      <c r="AR8" s="92" t="s">
+      <c r="AN8" s="86"/>
+      <c r="AO8" s="86"/>
+      <c r="AP8" s="86"/>
+      <c r="AQ8" s="86"/>
+      <c r="AR8" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="AS8" s="93"/>
-      <c r="AT8" s="93"/>
-      <c r="AU8" s="93"/>
-      <c r="AV8" s="93"/>
-      <c r="AW8" s="97" t="s">
+      <c r="AS8" s="86"/>
+      <c r="AT8" s="86"/>
+      <c r="AU8" s="86"/>
+      <c r="AV8" s="86"/>
+      <c r="AW8" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="AX8" s="98"/>
-      <c r="AY8" s="98"/>
-      <c r="AZ8" s="98"/>
-      <c r="BA8" s="98"/>
-      <c r="BB8" s="97" t="s">
+      <c r="AX8" s="88"/>
+      <c r="AY8" s="88"/>
+      <c r="AZ8" s="88"/>
+      <c r="BA8" s="88"/>
+      <c r="BB8" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="BC8" s="98"/>
-      <c r="BD8" s="98"/>
-      <c r="BE8" s="98"/>
-      <c r="BF8" s="98"/>
-      <c r="BG8" s="97" t="s">
+      <c r="BC8" s="88"/>
+      <c r="BD8" s="88"/>
+      <c r="BE8" s="88"/>
+      <c r="BF8" s="88"/>
+      <c r="BG8" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="BH8" s="98"/>
-      <c r="BI8" s="98"/>
-      <c r="BJ8" s="98"/>
-      <c r="BK8" s="98"/>
-      <c r="BL8" s="97" t="s">
+      <c r="BH8" s="88"/>
+      <c r="BI8" s="88"/>
+      <c r="BJ8" s="88"/>
+      <c r="BK8" s="88"/>
+      <c r="BL8" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="BM8" s="98"/>
-      <c r="BN8" s="98"/>
-      <c r="BO8" s="98"/>
-      <c r="BP8" s="98"/>
-      <c r="BQ8" s="102" t="s">
+      <c r="BM8" s="88"/>
+      <c r="BN8" s="88"/>
+      <c r="BO8" s="88"/>
+      <c r="BP8" s="88"/>
+      <c r="BQ8" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="BR8" s="103"/>
-      <c r="BS8" s="103"/>
-      <c r="BT8" s="103"/>
-      <c r="BU8" s="103"/>
-      <c r="BV8" s="102" t="s">
+      <c r="BR8" s="82"/>
+      <c r="BS8" s="82"/>
+      <c r="BT8" s="82"/>
+      <c r="BU8" s="82"/>
+      <c r="BV8" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="BW8" s="103"/>
-      <c r="BX8" s="103"/>
-      <c r="BY8" s="103"/>
-      <c r="BZ8" s="103"/>
-      <c r="CA8" s="102" t="s">
+      <c r="BW8" s="82"/>
+      <c r="BX8" s="82"/>
+      <c r="BY8" s="82"/>
+      <c r="BZ8" s="82"/>
+      <c r="CA8" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="CB8" s="103"/>
-      <c r="CC8" s="103"/>
-      <c r="CD8" s="103"/>
-      <c r="CE8" s="103"/>
+      <c r="CB8" s="82"/>
+      <c r="CC8" s="82"/>
+      <c r="CD8" s="82"/>
+      <c r="CE8" s="82"/>
       <c r="CF8" s="106" t="s">
         <v>50</v>
       </c>
@@ -2123,13 +2123,13 @@
       <c r="CH8" s="107"/>
       <c r="CI8" s="107"/>
       <c r="CJ8" s="108"/>
-      <c r="CK8" s="81" t="s">
+      <c r="CK8" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="CL8" s="82"/>
-      <c r="CM8" s="82"/>
-      <c r="CN8" s="82"/>
-      <c r="CO8" s="83"/>
+      <c r="CL8" s="90"/>
+      <c r="CM8" s="90"/>
+      <c r="CN8" s="90"/>
+      <c r="CO8" s="91"/>
       <c r="CP8" s="57"/>
     </row>
     <row r="9" spans="2:94" ht="20.100000000000001" customHeight="1" thickBot="1">
@@ -4463,7 +4463,7 @@
         <v>98</v>
       </c>
       <c r="H26" s="69">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I26" s="38"/>
       <c r="J26" s="21"/>
@@ -4592,7 +4592,7 @@
         <v>98</v>
       </c>
       <c r="H27" s="69">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I27" s="38"/>
       <c r="J27" s="21"/>
@@ -5200,7 +5200,7 @@
         <v>123</v>
       </c>
       <c r="H32" s="69">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I32" s="38"/>
       <c r="J32" s="21"/>
@@ -5549,7 +5549,7 @@
         <v>133</v>
       </c>
       <c r="H35" s="69">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I35" s="38"/>
       <c r="J35" s="21"/>
@@ -6354,12 +6354,6 @@
   </sheetData>
   <autoFilter ref="D1:D45" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <mergeCells count="22">
-    <mergeCell ref="BV8:BZ8"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="AC8:AG8"/>
-    <mergeCell ref="AH8:AL8"/>
-    <mergeCell ref="AR8:AV8"/>
-    <mergeCell ref="AW8:BA8"/>
     <mergeCell ref="CK8:CO8"/>
     <mergeCell ref="I7:AB7"/>
     <mergeCell ref="X8:AB8"/>
@@ -6376,6 +6370,12 @@
     <mergeCell ref="BB8:BF8"/>
     <mergeCell ref="BL8:BP8"/>
     <mergeCell ref="BQ8:BU8"/>
+    <mergeCell ref="BV8:BZ8"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="AC8:AG8"/>
+    <mergeCell ref="AH8:AL8"/>
+    <mergeCell ref="AR8:AV8"/>
+    <mergeCell ref="AW8:BA8"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="D37:G37">
